--- a/data/trans_dic/IP24_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,79</t>
+          <t>7,07; 20,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 18,92</t>
+          <t>7,79; 21,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 16,05</t>
+          <t>9,0; 19,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>2,58; 11,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,14</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,45</t>
+          <t>2,07; 7,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>9,03%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,98</t>
+          <t>7,51; 22,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 21,03</t>
+          <t>4,25; 16,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 17,18</t>
+          <t>7,22; 16,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,62</t>
+          <t>5,52; 26,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 24,46</t>
+          <t>0,71; 8,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 14,79</t>
+          <t>4,09; 15,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,32; 60,61</t>
+          <t>38,74; 63,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,84; 61,99</t>
+          <t>37,86; 63,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,27; 57,86</t>
+          <t>43,47; 60,07</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 25,09</t>
+          <t>18,82; 32,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,37; 30,88</t>
+          <t>9,82; 21,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,78; 25,54</t>
+          <t>16,68; 25,61</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>1,81; 8,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,0</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,75</t>
+          <t>1,3; 4,68</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,96</t>
+          <t>11,37; 16,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,15</t>
+          <t>7,13; 10,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,27</t>
+          <t>9,79; 12,88</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>15970</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4059; 13035</t>
+          <t>4534; 13259</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4793; 15019</t>
+          <t>4400; 12273</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11651; 24496</t>
+          <t>10853; 23065</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9057</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6221</t>
+          <t>2934; 13366</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3175; 13891</t>
+          <t>0; 6509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4216; 16197</t>
+          <t>4434; 15556</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>13064</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2520; 9892</t>
+          <t>4458; 13253</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5119; 14123</t>
+          <t>2403; 9253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8982; 21543</t>
+          <t>8371; 19198</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11378</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>554; 6044</t>
+          <t>3982; 18938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3624; 19112</t>
+          <t>503; 5768</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5539; 21924</t>
+          <t>5847; 22872</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>38268</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12882; 20918</t>
+          <t>15331; 25218</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15002; 25242</t>
+          <t>13482; 22472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30293; 43532</t>
+          <t>32687; 45168</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>53836</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13325; 30950</t>
+          <t>26362; 45856</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26867; 47771</t>
+          <t>11939; 26178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43882; 71027</t>
+          <t>43646; 67016</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7755</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5217</t>
+          <t>2883; 13025</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2839; 12546</t>
+          <t>0; 4879</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4076; 13714</t>
+          <t>3913; 14033</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>44882; 72726</t>
+          <t>79290; 113187</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>81121; 114773</t>
+          <t>44740; 67125</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131762; 174382</t>
+          <t>129735; 170692</t>
         </is>
       </c>
     </row>
